--- a/output/pdf_financials_xlsx/KBX.xlsx
+++ b/output/pdf_financials_xlsx/KBX.xlsx
@@ -2067,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.639238</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.167419</v>
       </c>
     </row>
     <row r="93">
@@ -2899,7 +2899,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -3285,7 +3289,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4377,7 +4385,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -5995,7 +6007,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KBX.xlsx
+++ b/output/pdf_financials_xlsx/KBX.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.383958</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.473098</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.42787</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.383958</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.473098</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.42787</v>
       </c>
     </row>
     <row r="37">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.383958</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.863705</v>
+        <v>0.390607</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>7.74563</v>
+        <v>0.31776</v>
       </c>
     </row>
     <row r="49">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/KBX.xlsx
+++ b/output/pdf_financials_xlsx/KBX.xlsx
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.005473</v>
       </c>
     </row>
     <row r="111">
@@ -5274,7 +5274,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
